--- a/data/trans_orig/P1431-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1431-Estudios-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de enfermedad de riñón en 2012</t>
+          <t>Población con diagnóstico de enfermedad de riñón en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15669</t>
+          <t>15400</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35813</t>
+          <t>36142</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21466</t>
+          <t>21240</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44269</t>
+          <t>45218</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>42379</t>
+          <t>42479</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>71913</t>
+          <t>73013</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>938830</t>
+          <t>938501</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>958974</t>
+          <t>959243</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1292419</t>
+          <t>1291470</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1315222</t>
+          <t>1315448</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2239418</t>
+          <t>2238318</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2268952</t>
+          <t>2268852</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,16%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8295</t>
+          <t>8553</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24355</t>
+          <t>24818</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10373</t>
+          <t>10478</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26570</t>
+          <t>27254</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22293</t>
+          <t>22252</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>44511</t>
+          <t>44926</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1939602</t>
+          <t>1939139</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1955662</t>
+          <t>1955404</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1728022</t>
+          <t>1727338</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1744219</t>
+          <t>1744114</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3674038</t>
+          <t>3673623</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3696256</t>
+          <t>3696297</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6650</t>
+          <t>5627</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>970</t>
+          <t>968</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10321</t>
+          <t>11204</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1894</t>
+          <t>1880</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12313</t>
+          <t>12187</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>474531</t>
+          <t>475554</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>448310</t>
+          <t>447427</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>457661</t>
+          <t>457663</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>927500</t>
+          <t>927626</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>937919</t>
+          <t>937933</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28978</t>
+          <t>29246</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>56924</t>
+          <t>56496</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40132</t>
+          <t>39443</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>68191</t>
+          <t>68888</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>75353</t>
+          <t>74595</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>115420</t>
+          <t>114887</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3362858</t>
+          <t>3363286</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3390804</t>
+          <t>3390536</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3481720</t>
+          <t>3481023</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3509779</t>
+          <t>3510468</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6854273</t>
+          <t>6854806</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6894340</t>
+          <t>6895098</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,93%</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de enfermedad de riñón en 2016</t>
+          <t>Población con diagnóstico de enfermedad de riñón en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2334,12 +2334,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6361</t>
+          <t>6572</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19235</t>
+          <t>20560</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2349,12 +2349,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25359</t>
+          <t>24193</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>51116</t>
+          <t>48534</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2404,12 +2404,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34180</t>
+          <t>35043</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>63244</t>
+          <t>63449</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2419,12 +2419,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>735112</t>
+          <t>733787</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>747986</t>
+          <t>747775</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>943544</t>
+          <t>946126</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>969301</t>
+          <t>970467</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1685763</t>
+          <t>1685558</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1714827</t>
+          <t>1713964</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,0%</t>
         </is>
       </c>
     </row>
@@ -2677,12 +2677,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17211</t>
+          <t>17595</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39165</t>
+          <t>37884</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2712,12 +2712,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10993</t>
+          <t>11439</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29024</t>
+          <t>28115</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2727,12 +2727,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2747,12 +2747,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31430</t>
+          <t>31952</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>57986</t>
+          <t>58159</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2762,7 +2762,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2037220</t>
+          <t>2038501</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2059174</t>
+          <t>2058790</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1959276</t>
+          <t>1960185</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1977307</t>
+          <t>1976861</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4006699</t>
+          <t>4006526</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4033255</t>
+          <t>4032733</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,21%</t>
         </is>
       </c>
     </row>
@@ -3020,12 +3020,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3313</t>
+          <t>3287</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16256</t>
+          <t>16988</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3035,12 +3035,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6779</t>
+          <t>6799</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5122</t>
+          <t>4805</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19592</t>
+          <t>19059</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3105,12 +3105,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>530630</t>
+          <t>529898</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>543573</t>
+          <t>543599</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>542361</t>
+          <t>542341</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1076435</t>
+          <t>1076968</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1090905</t>
+          <t>1091222</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,56%</t>
         </is>
       </c>
     </row>
@@ -3363,12 +3363,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33409</t>
+          <t>33255</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>60181</t>
+          <t>61594</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3378,12 +3378,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>43264</t>
+          <t>42970</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72057</t>
+          <t>74175</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>82776</t>
+          <t>83612</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>123280</t>
+          <t>123006</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3317437</t>
+          <t>3316024</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3344209</t>
+          <t>3344363</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3491,82 +3491,82 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>98,18%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,02%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>3275</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>3475274</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>3457925</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3489130</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>98,39%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>97,9%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>98,78%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>6445</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>6807420</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>6786712</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>6826106</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>98,52%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>98,22%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,01%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>3275</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>3475274</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>3460043</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>3488836</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,39%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>97,96%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>98,78%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>6445</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>6807420</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>6786438</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>6826942</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>98,52%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>98,22%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,79%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1431-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1431-Estudios-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15400</t>
+          <t>14480</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36142</t>
+          <t>34564</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21240</t>
+          <t>22170</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>45218</t>
+          <t>44514</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>42479</t>
+          <t>43359</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>73013</t>
+          <t>72144</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>938501</t>
+          <t>940079</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>959243</t>
+          <t>960163</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1291470</t>
+          <t>1292174</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1315448</t>
+          <t>1314518</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2238318</t>
+          <t>2239187</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2268852</t>
+          <t>2267972</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,12%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8553</t>
+          <t>8534</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24818</t>
+          <t>24901</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10478</t>
+          <t>10081</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27254</t>
+          <t>25678</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,47 +1124,47 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>32380</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>22451</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>45605</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,87%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>0,6%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>32380</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>22252</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>44926</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1939139</t>
+          <t>1939056</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1955404</t>
+          <t>1955423</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1727338</t>
+          <t>1728914</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1744114</t>
+          <t>1744511</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3673623</t>
+          <t>3672944</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3696297</t>
+          <t>3696098</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5627</t>
+          <t>5630</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>974</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11204</t>
+          <t>11239</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1880</t>
+          <t>1974</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12187</t>
+          <t>14181</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>475554</t>
+          <t>475551</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>447427</t>
+          <t>447392</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>457663</t>
+          <t>457657</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>927626</t>
+          <t>925632</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>937933</t>
+          <t>937839</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,79%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29246</t>
+          <t>28673</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>56496</t>
+          <t>56100</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>39443</t>
+          <t>39325</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>68888</t>
+          <t>68359</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>74595</t>
+          <t>75457</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>114887</t>
+          <t>115474</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3363286</t>
+          <t>3363682</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3390536</t>
+          <t>3391109</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3481023</t>
+          <t>3481552</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3510468</t>
+          <t>3510586</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6854806</t>
+          <t>6854219</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6895098</t>
+          <t>6894236</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,92%</t>
         </is>
       </c>
     </row>
@@ -2334,12 +2334,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6572</t>
+          <t>6436</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20560</t>
+          <t>18866</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2349,77 +2349,77 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>2,5%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>35977</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>25086</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>48938</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>3,62%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>2,52%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>4,92%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>47818</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>36189</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>63523</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
           <t>2,73%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>35977</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>24193</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>48534</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>3,62%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>2,43%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>4,88%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>47818</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>35043</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>63449</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>2,73%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>733787</t>
+          <t>735481</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>747775</t>
+          <t>747911</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2462,74 +2462,74 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>97,5%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>99,15%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>860</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>958683</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>945722</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>969574</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>96,38%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>95,08%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>97,48%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>1609</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>1701189</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>1685484</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>1712818</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
           <t>97,27%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>99,13%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>860</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>958683</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>946126</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>970467</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>96,38%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>95,12%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>97,57%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1609</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>1701189</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>1685558</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>1713964</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>97,27%</t>
-        </is>
-      </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
           <t>96,37%</t>
@@ -2537,7 +2537,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,93%</t>
         </is>
       </c>
     </row>
@@ -2677,12 +2677,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17595</t>
+          <t>17108</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37884</t>
+          <t>37618</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2712,12 +2712,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11439</t>
+          <t>10889</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28115</t>
+          <t>27559</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2727,12 +2727,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2747,12 +2747,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31952</t>
+          <t>33018</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>58159</t>
+          <t>58896</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2762,12 +2762,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2038501</t>
+          <t>2038767</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2058790</t>
+          <t>2059277</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1960185</t>
+          <t>1960741</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1976861</t>
+          <t>1977411</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4006526</t>
+          <t>4005789</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4032733</t>
+          <t>4031667</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,19%</t>
         </is>
       </c>
     </row>
@@ -3020,12 +3020,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3287</t>
+          <t>3617</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16988</t>
+          <t>16468</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3035,12 +3035,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6799</t>
+          <t>7396</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4805</t>
+          <t>4594</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19059</t>
+          <t>18298</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3105,12 +3105,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>529898</t>
+          <t>530418</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>543599</t>
+          <t>543269</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>542341</t>
+          <t>541744</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1076968</t>
+          <t>1077729</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1091222</t>
+          <t>1091433</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,58%</t>
         </is>
       </c>
     </row>
@@ -3363,12 +3363,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33255</t>
+          <t>33459</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>61594</t>
+          <t>60896</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3378,12 +3378,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>42970</t>
+          <t>43509</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>74175</t>
+          <t>74209</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3413,7 +3413,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>83612</t>
+          <t>82278</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>123006</t>
+          <t>123315</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3316024</t>
+          <t>3316722</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3344363</t>
+          <t>3344159</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3457925</t>
+          <t>3457891</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3489130</t>
+          <t>3488591</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6786712</t>
+          <t>6786403</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6826106</t>
+          <t>6827440</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,81%</t>
         </is>
       </c>
     </row>
